--- a/bootcamp/Bootcamp_Schedule.xlsx
+++ b/bootcamp/Bootcamp_Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rashap/Documents/Quantum/Quantum/bootcamp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A315A8EA-2F5D-B047-829A-0375C20BE6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372DAC2F-88AE-B645-84AE-FBE6F37BFDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="1320" windowWidth="29400" windowHeight="16800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="1320" windowWidth="29400" windowHeight="16800" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="159">
   <si>
     <t>Orientation &amp; FUSE Tour</t>
   </si>
@@ -571,6 +571,26 @@
   <si>
     <t>UHV Fundamentals</t>
   </si>
+  <si>
+    <t>QKD Introduction</t>
+  </si>
+  <si>
+    <t>Free Space to Fiber Coupling</t>
+  </si>
+  <si>
+    <t>Two Mirror Walk Revisited</t>
+  </si>
+  <si>
+    <t>ProDev - 
+Constructive Confrontation</t>
+  </si>
+  <si>
+    <t>Linear Algebra
+Quantum Gates</t>
+  </si>
+  <si>
+    <t>IBM Quantum Composer Quantum Teleportation</t>
+  </si>
 </sst>
 </file>
 
@@ -815,7 +835,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -922,67 +942,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1017,6 +984,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1245,10 +1221,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="36" t="s">
@@ -29811,10 +29787,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="36" t="s">
@@ -29859,19 +29835,19 @@
       <c r="B2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="43" t="s">
         <v>113</v>
       </c>
       <c r="H2" s="3"/>
@@ -29903,17 +29879,17 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="60"/>
-      <c r="E3" s="62" t="s">
+      <c r="D3" s="41"/>
+      <c r="E3" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="60"/>
+      <c r="G3" s="41"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -29943,11 +29919,11 @@
         <f t="shared" si="1"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -29977,11 +29953,11 @@
         <f t="shared" si="2"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -30011,11 +29987,11 @@
         <f t="shared" si="3"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -30045,13 +30021,13 @@
         <f t="shared" si="4"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="62" t="s">
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -30081,11 +30057,11 @@
         <f t="shared" si="5"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -30115,15 +30091,15 @@
         <f t="shared" si="6"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="62" t="s">
+      <c r="D9" s="41"/>
+      <c r="E9" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -30153,13 +30129,13 @@
         <f t="shared" si="7"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="60"/>
-      <c r="D10" s="62" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -30189,15 +30165,15 @@
         <f t="shared" si="8"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="62" t="s">
+      <c r="D11" s="41"/>
+      <c r="E11" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -30227,11 +30203,11 @@
         <f t="shared" si="9"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -30261,15 +30237,15 @@
         <f t="shared" si="10"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="62" t="s">
+      <c r="C13" s="41"/>
+      <c r="D13" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="60"/>
-      <c r="F13" s="62" t="s">
+      <c r="E13" s="41"/>
+      <c r="F13" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="60"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -30299,13 +30275,13 @@
         <f t="shared" si="11"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -30335,15 +30311,15 @@
         <f t="shared" si="12"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="60"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -30373,11 +30349,11 @@
         <f t="shared" si="13"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -30407,13 +30383,13 @@
         <f t="shared" si="14"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="62" t="s">
+      <c r="C17" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="62"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -30443,13 +30419,13 @@
         <f t="shared" si="15"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="62" t="s">
+      <c r="C18" s="41"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="G18" s="60"/>
+      <c r="G18" s="41"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -30479,11 +30455,11 @@
         <f t="shared" si="16"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -58011,10 +57987,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="36" t="s">
@@ -58059,19 +58035,19 @@
       <c r="B2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="43" t="s">
         <v>24</v>
       </c>
     </row>
@@ -58084,17 +58060,17 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="68"/>
-      <c r="E3" s="62" t="s">
+      <c r="D3" s="49"/>
+      <c r="E3" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="68"/>
+      <c r="G3" s="49"/>
     </row>
     <row r="4" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10">
@@ -58105,13 +58081,13 @@
         <f t="shared" si="1"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="62" t="s">
+      <c r="C4" s="49"/>
+      <c r="D4" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -58123,11 +58099,11 @@
         <f t="shared" si="2"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10">
@@ -58138,15 +58114,15 @@
         <f t="shared" si="3"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="62" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
     </row>
     <row r="7" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10">
@@ -58157,11 +58133,11 @@
         <f t="shared" si="4"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10">
@@ -58172,13 +58148,13 @@
         <f t="shared" si="5"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="62" t="s">
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="68"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10">
@@ -58189,11 +58165,11 @@
         <f t="shared" si="6"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
@@ -58204,19 +58180,19 @@
         <f t="shared" si="7"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="43" t="s">
         <v>12</v>
       </c>
     </row>
@@ -58229,11 +58205,11 @@
         <f t="shared" si="8"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
     </row>
     <row r="12" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
@@ -58244,19 +58220,19 @@
         <f t="shared" si="9"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="D12" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="E12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="43" t="s">
         <v>50</v>
       </c>
     </row>
@@ -58269,11 +58245,11 @@
         <f t="shared" si="10"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
     </row>
     <row r="14" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
@@ -58284,11 +58260,11 @@
         <f t="shared" si="11"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="15" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
@@ -58299,11 +58275,11 @@
         <f t="shared" si="12"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="65" t="s">
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="46" t="s">
         <v>51</v>
       </c>
     </row>
@@ -58316,13 +58292,13 @@
         <f t="shared" si="13"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="62" t="s">
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="67" t="s">
+      <c r="G16" s="48" t="s">
         <v>53</v>
       </c>
     </row>
@@ -58335,13 +58311,13 @@
         <f t="shared" si="14"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="62" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="68"/>
-      <c r="G17" s="70"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
@@ -58352,13 +58328,13 @@
         <f t="shared" si="15"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="62" t="s">
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="70"/>
+      <c r="G18" s="51"/>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
@@ -58369,11 +58345,11 @@
         <f t="shared" si="16"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="70"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -58419,25 +58395,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="45" t="s">
         <v>41</v>
       </c>
     </row>
@@ -58448,19 +58424,19 @@
       <c r="B2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="69" t="s">
+      <c r="G2" s="50" t="s">
         <v>23</v>
       </c>
     </row>
@@ -58473,17 +58449,17 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="49"/>
+      <c r="G3" s="43" t="s">
         <v>60</v>
       </c>
     </row>
@@ -58496,15 +58472,15 @@
         <f t="shared" si="1"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="62" t="s">
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="68"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10">
@@ -58515,11 +58491,11 @@
         <f t="shared" si="2"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10">
@@ -58530,13 +58506,13 @@
         <f t="shared" si="3"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="62" t="s">
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="68"/>
-      <c r="G6" s="69" t="s">
+      <c r="F6" s="49"/>
+      <c r="G6" s="50" t="s">
         <v>64</v>
       </c>
     </row>
@@ -58549,13 +58525,13 @@
         <f t="shared" si="4"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="C7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="62" t="s">
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="43" t="s">
         <v>66</v>
       </c>
     </row>
@@ -58568,11 +58544,11 @@
         <f t="shared" si="5"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
     </row>
     <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10">
@@ -58583,11 +58559,11 @@
         <f t="shared" si="6"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
@@ -58598,19 +58574,19 @@
         <f t="shared" si="7"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="43" t="s">
         <v>12</v>
       </c>
     </row>
@@ -58623,11 +58599,11 @@
         <f t="shared" si="8"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
     </row>
     <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
@@ -58638,17 +58614,17 @@
         <f t="shared" si="9"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="62" t="s">
+      <c r="D12" s="49"/>
+      <c r="E12" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="F12" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="43" t="s">
         <v>68</v>
       </c>
     </row>
@@ -58661,13 +58637,13 @@
         <f t="shared" si="10"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="D13" s="62" t="s">
+      <c r="C13" s="49"/>
+      <c r="D13" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
     </row>
     <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
@@ -58678,11 +58654,11 @@
         <f t="shared" si="11"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
@@ -58693,13 +58669,13 @@
         <f t="shared" si="12"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="62" t="s">
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G15" s="48" t="s">
         <v>53</v>
       </c>
     </row>
@@ -58712,11 +58688,11 @@
         <f t="shared" si="13"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
     </row>
     <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
@@ -58727,17 +58703,17 @@
         <f t="shared" si="14"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="68"/>
-      <c r="D17" s="62" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="62" t="s">
+      <c r="E17" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="62" t="s">
+      <c r="F17" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="49"/>
     </row>
     <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
@@ -58748,13 +58724,13 @@
         <f t="shared" si="15"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
@@ -58765,11 +58741,11 @@
         <f t="shared" si="16"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -58817,10 +58793,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="36" t="s">
@@ -58846,19 +58822,19 @@
       <c r="B2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -58871,19 +58847,19 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="42" t="s">
         <v>134</v>
       </c>
     </row>
@@ -58896,11 +58872,11 @@
         <f t="shared" si="1"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10">
@@ -58911,11 +58887,11 @@
         <f t="shared" si="2"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10">
@@ -58926,13 +58902,15 @@
         <f t="shared" si="3"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="70"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10">
@@ -58943,11 +58921,11 @@
         <f t="shared" si="4"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="70"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10">
@@ -58958,15 +58936,15 @@
         <f t="shared" si="5"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="62" t="s">
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="70"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10">
@@ -58977,11 +58955,11 @@
         <f t="shared" si="6"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="70"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
@@ -58992,17 +58970,17 @@
         <f t="shared" si="7"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="63"/>
-      <c r="F10" s="62" t="s">
+      <c r="E10" s="44"/>
+      <c r="F10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="43" t="s">
         <v>12</v>
       </c>
     </row>
@@ -59015,13 +58993,13 @@
         <f t="shared" si="8"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="62" t="s">
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
@@ -59032,17 +59010,19 @@
         <f t="shared" si="9"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="D12" s="42" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="63"/>
-      <c r="F12" s="62" t="s">
+      <c r="E12" s="44"/>
+      <c r="F12" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="70"/>
+      <c r="G12" s="42" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10">
@@ -59053,11 +59033,11 @@
         <f t="shared" si="10"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="70"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
@@ -59068,11 +59048,11 @@
         <f t="shared" si="11"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="70"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
@@ -59083,11 +59063,11 @@
         <f t="shared" si="12"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="67" t="s">
+      <c r="C15" s="52"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="48" t="s">
         <v>53</v>
       </c>
     </row>
@@ -59100,11 +59080,11 @@
         <f t="shared" si="13"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="71"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="68"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="49"/>
     </row>
     <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
@@ -59115,11 +59095,11 @@
         <f t="shared" si="14"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="68"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="49"/>
     </row>
     <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
@@ -59130,13 +59110,13 @@
         <f t="shared" si="15"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="62" t="s">
+      <c r="C18" s="52"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="68"/>
+      <c r="G18" s="49"/>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
@@ -59147,11 +59127,11 @@
         <f t="shared" si="16"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="68"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="49"/>
     </row>
     <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="9"/>
@@ -59200,25 +59180,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="G1" s="45" t="s">
         <v>41</v>
       </c>
     </row>
@@ -59229,19 +59209,19 @@
       <c r="B2" s="10">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="65" t="s">
+      <c r="G2" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -59254,19 +59234,19 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="61" t="s">
+      <c r="E3" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="61" t="s">
+      <c r="F3" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="G3" s="61" t="s">
+      <c r="G3" s="42" t="s">
         <v>152</v>
       </c>
     </row>
@@ -59279,13 +59259,13 @@
         <f t="shared" si="1"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="63"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
     </row>
     <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10">
@@ -59296,11 +59276,11 @@
         <f t="shared" si="2"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
     </row>
     <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10">
@@ -59311,15 +59291,15 @@
         <f t="shared" si="3"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="62" t="s">
+      <c r="C6" s="44"/>
+      <c r="D6" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61" t="s">
+      <c r="E6" s="42"/>
+      <c r="F6" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="61"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10">
@@ -59330,13 +59310,13 @@
         <f t="shared" si="4"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="61" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
     </row>
     <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10">
@@ -59347,13 +59327,13 @@
         <f t="shared" si="5"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="63"/>
-      <c r="D8" s="62" t="s">
+      <c r="C8" s="44"/>
+      <c r="D8" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10">
@@ -59364,11 +59344,11 @@
         <f t="shared" si="6"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
@@ -59379,19 +59359,19 @@
         <f t="shared" si="7"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="62" t="s">
+      <c r="C10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="E10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="62" t="s">
+      <c r="F10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="43" t="s">
         <v>12</v>
       </c>
     </row>
@@ -59404,11 +59384,11 @@
         <f t="shared" si="8"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="66"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
@@ -59419,19 +59399,19 @@
         <f t="shared" si="9"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="D12" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="F12" s="61" t="s">
+      <c r="F12" s="42" t="s">
         <v>142</v>
       </c>
-      <c r="G12" s="61" t="s">
+      <c r="G12" s="42" t="s">
         <v>152</v>
       </c>
     </row>
@@ -59444,11 +59424,11 @@
         <f t="shared" si="10"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
@@ -59459,13 +59439,13 @@
         <f t="shared" si="11"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
     </row>
     <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
@@ -59476,11 +59456,11 @@
         <f t="shared" si="12"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="67" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="48" t="s">
         <v>53</v>
       </c>
     </row>
@@ -59493,13 +59473,13 @@
         <f t="shared" si="13"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="61" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="68"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="49"/>
     </row>
     <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
@@ -59510,15 +59490,15 @@
         <f t="shared" si="14"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="63"/>
-      <c r="D17" s="62" t="s">
+      <c r="C17" s="44"/>
+      <c r="D17" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="61"/>
-      <c r="F17" s="62" t="s">
+      <c r="E17" s="42"/>
+      <c r="F17" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="49"/>
     </row>
     <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
@@ -59529,11 +59509,11 @@
         <f t="shared" si="15"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="68"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="49"/>
     </row>
     <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
@@ -59544,11 +59524,11 @@
         <f t="shared" si="16"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="68"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -59596,10 +59576,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="38" t="s">
         <v>149</v>
       </c>
       <c r="C1" s="36" t="s">
@@ -59641,7 +59621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10">
         <f t="shared" ref="A3:B18" si="0">A2+TIME(0,30,0)</f>
         <v>0.35416666666666663</v>
@@ -59650,17 +59630,23 @@
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="40" t="s">
+      <c r="C3" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="42" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10">
         <f t="shared" si="0"/>
         <v>0.37499999999999994</v>
@@ -59669,13 +59655,13 @@
         <f t="shared" si="0"/>
         <v>0.39583333333333331</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="54"/>
-    </row>
-    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="42"/>
+    </row>
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10">
         <f t="shared" si="0"/>
         <v>0.39583333333333326</v>
@@ -59684,15 +59670,15 @@
         <f t="shared" si="0"/>
         <v>0.41666666666666663</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="41" t="s">
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="40" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>0.41666666666666657</v>
@@ -59701,15 +59687,15 @@
         <f t="shared" si="0"/>
         <v>0.43749999999999994</v>
       </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="42" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="45"/>
-    </row>
-    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F6" s="53"/>
+      <c r="G6" s="40"/>
+    </row>
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>0.43749999999999989</v>
@@ -59718,13 +59704,13 @@
         <f t="shared" si="0"/>
         <v>0.45833333333333326</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="45"/>
-    </row>
-    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="40"/>
+    </row>
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>0.4583333333333332</v>
@@ -59733,13 +59719,13 @@
         <f t="shared" si="0"/>
         <v>0.47916666666666657</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="45"/>
-    </row>
-    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>0.47916666666666652</v>
@@ -59748,11 +59734,11 @@
         <f t="shared" si="0"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="44"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10">
@@ -59763,19 +59749,19 @@
         <f t="shared" si="0"/>
         <v>0.52083333333333326</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="39" t="s">
         <v>12</v>
       </c>
     </row>
@@ -59788,13 +59774,13 @@
         <f t="shared" si="0"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-    </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+    </row>
+    <row r="12" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>0.54166666666666652</v>
@@ -59803,21 +59789,23 @@
         <f t="shared" si="0"/>
         <v>0.5625</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="40" t="s">
+      <c r="D12" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="49" t="s">
+      <c r="G12" s="42" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>0.56249999999999989</v>
@@ -59826,13 +59814,13 @@
         <f t="shared" si="0"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="52"/>
-    </row>
-    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="43"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="42"/>
+    </row>
+    <row r="14" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>0.58333333333333326</v>
@@ -59841,13 +59829,13 @@
         <f t="shared" si="0"/>
         <v>0.60416666666666674</v>
       </c>
-      <c r="C14" s="50"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="54"/>
-    </row>
-    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="43"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="42"/>
+    </row>
+    <row r="15" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>0.60416666666666663</v>
@@ -59856,15 +59844,17 @@
         <f t="shared" si="0"/>
         <v>0.62500000000000011</v>
       </c>
-      <c r="C15" s="50"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="40" t="s">
+      <c r="C15" s="43"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="55"/>
-    </row>
-    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F15" s="53"/>
+      <c r="G15" s="55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10">
         <f t="shared" si="0"/>
         <v>0.625</v>
@@ -59873,13 +59863,15 @@
         <f t="shared" si="0"/>
         <v>0.64583333333333348</v>
       </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="55"/>
     </row>
-    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10">
         <f t="shared" si="0"/>
         <v>0.64583333333333337</v>
@@ -59888,13 +59880,15 @@
         <f t="shared" si="0"/>
         <v>0.66666666666666685</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
+      <c r="C17" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="40"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
       <c r="G17" s="55"/>
     </row>
-    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10">
         <f t="shared" si="0"/>
         <v>0.66666666666666674</v>
@@ -59903,13 +59897,13 @@
         <f t="shared" si="0"/>
         <v>0.68750000000000022</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
       <c r="G18" s="55"/>
     </row>
-    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10">
         <f t="shared" ref="A19:B19" si="1">A18+TIME(0,30,0)</f>
         <v>0.68750000000000011</v>
@@ -59918,10 +59912,10 @@
         <f t="shared" si="1"/>
         <v>0.70833333333333359</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="55"/>
     </row>
     <row r="22" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -59935,7 +59929,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D3:D9"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="D12:D15"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="F10:F11"/>
@@ -59951,6 +59950,7 @@
     <mergeCell ref="E15:E19"/>
     <mergeCell ref="G5:G9"/>
     <mergeCell ref="E6:E9"/>
+    <mergeCell ref="E3:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="61" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
